--- a/jogos_2025-02-25.xlsx
+++ b/jogos_2025-02-25.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9.81</v>
+        <v>2.11</v>
       </c>
       <c r="M7" t="n">
-        <v>7.98</v>
+        <v>3.21</v>
       </c>
       <c r="N7" t="n">
-        <v>1.17</v>
+        <v>3.53</v>
       </c>
       <c r="O7" t="n">
-        <v>6.6</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>4.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.68</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="n">
-        <v>5.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.47</v>
+        <v>2.94</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.6</v>
+        <v>1.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.91</v>
+        <v>5.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.86</v>
+        <v>1.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>['21', '34']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['48', '90+10']</t>
-        </is>
-      </c>
       <c r="AG7" t="n">
-        <v>2.95</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45713.58333333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,65 +1443,65 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.11</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.67</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.94</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.6</v>
+        <v>2.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['21', '34']</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>1.16</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>2.79</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.1</v>
+        <v>1.46</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45713.58333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>9.81</v>
       </c>
       <c r="M9" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['48', '90+10']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI9" t="n">
         <v>3.2</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="AJ9" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['32', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45713.58333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>4.33</v>
+        <v>3.73</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AD10" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['32', '90+3']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>2.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.79</v>
+        <v>1.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.46</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45713.58333333334</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.3</v>
       </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
       <c r="Q11" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>4.19</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['11', '27', '42', '52']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['21', '37']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['26']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45713.60416666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.57</v>
-      </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
-        <v>4.19</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.71</v>
+        <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['11', '27', '42', '52']</t>
+          <t>['21', '37']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['26']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45713.60416666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>3.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.86</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>1.95</v>
       </c>
       <c r="O16" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.46</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['53', '84']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45713.69791666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.91</v>
+        <v>3.53</v>
       </c>
       <c r="M17" t="n">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="N17" t="n">
-        <v>2.51</v>
+        <v>2.06</v>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['90', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['1', '79']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2.5</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['15', '42']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45713.69791666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
         <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.19</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="N18" t="n">
-        <v>3.23</v>
+        <v>2.74</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
         <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
         <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
         <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45713.69791666666</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>1</v>
       </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>2.19</v>
       </c>
       <c r="M19" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>2.61</v>
+        <v>3.23</v>
       </c>
       <c r="O19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X19" t="n">
         <v>3.25</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3</v>
-      </c>
       <c r="Y19" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['45', '50']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45713.69791666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N20" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
         <v>3.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['20', '52', '73']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
         <v>1.42</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45713.69791666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.53</v>
+        <v>1.57</v>
       </c>
       <c r="M21" t="n">
-        <v>3.32</v>
+        <v>3.86</v>
       </c>
       <c r="N21" t="n">
-        <v>2.06</v>
+        <v>5.7</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.63</v>
+        <v>6.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
         <v>1.05</v>
       </c>
       <c r="W21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.28</v>
       </c>
-      <c r="X21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['53', '84']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['90', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['1', '79']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45713.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.7</v>
+        <v>2.61</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.61</v>
       </c>
       <c r="O22" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['45', '50']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45713.69791666666</v>
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.51</v>
+        <v>2.91</v>
       </c>
       <c r="M23" t="n">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['15', '42']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['36', '59']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI23" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45713.69791666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.4</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['36', '59']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['29', '35', '37']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['28', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45713.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hamilton Academical</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3636,80 +3636,80 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.33</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="Y25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.73</v>
       </c>
       <c r="AJ25" t="n">
         <v>2.25</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Hamilton Academical</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.35</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['20', '52', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45713.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.49</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P27" t="n">
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['29', '35', '37']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '90+3']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.58</v>
+        <v>2.48</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45713.69791666666</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>10.67</v>
+        <v>9</v>
       </c>
       <c r="O31" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="P31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA31" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>9</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['41', '48', '63']</t>
+          <t>['5', '58']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AH31" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45713.89583333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="M32" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>9</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['41', '48', '63']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>4.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>7</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['5', '58']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>3.65</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45713.89583333334</v>
